--- a/VT_REG1_ELC_V12_Stock_2050.xlsx
+++ b/VT_REG1_ELC_V12_Stock_2050.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Veda\Veda_models\Demo_models\001_KHM_TIMES_20260606\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A0FADD-1399-40D3-8BA2-149781F8BD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BE6E50-C696-4293-9DF0-8EA7DAC885AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -6511,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="99">
-        <f>H12*$L12*$Q12</f>
+        <f t="shared" ref="T12:T18" si="2">H12*$L12*$Q12</f>
         <v>17.691696000000004</v>
       </c>
       <c r="U12" s="85"/>
@@ -6528,11 +6528,11 @@
         <v>Power Plants Existing00 - Solid Fuels</v>
       </c>
       <c r="Z12" s="94" t="str">
-        <f t="shared" ref="Z12:Z18" si="2">$E$2</f>
+        <f t="shared" ref="Z12:Z18" si="3">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="AA12" s="94" t="str">
-        <f t="shared" ref="AA12:AA18" si="3">$F$2</f>
+        <f t="shared" ref="AA12:AA18" si="4">$F$2</f>
         <v>GW</v>
       </c>
       <c r="AB12" s="90"/>
@@ -6580,7 +6580,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="99">
-        <f>H13*$L13*$Q13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U13" s="28"/>
@@ -6597,11 +6597,11 @@
         <v>Power Plants Existing00 - Natural Gas</v>
       </c>
       <c r="Z13" s="94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="AA13" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>GW</v>
       </c>
       <c r="AB13" s="94"/>
@@ -6649,7 +6649,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="99">
-        <f>H14*$L14*$Q14</f>
+        <f t="shared" si="2"/>
         <v>2.6376710399999999</v>
       </c>
       <c r="U14" s="28"/>
@@ -6666,11 +6666,11 @@
         <v>Power Plants Existing00 - Crude oil</v>
       </c>
       <c r="Z14" s="94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="AA14" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>GW</v>
       </c>
       <c r="AB14" s="94"/>
@@ -6718,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="99">
-        <f>H15*$L15*$Q15</f>
+        <f t="shared" si="2"/>
         <v>3.78432E-2</v>
       </c>
       <c r="U15" s="28"/>
@@ -6735,11 +6735,11 @@
         <v>Power Plants Existing00 - Biomass</v>
       </c>
       <c r="Z15" s="94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="AA15" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>GW</v>
       </c>
       <c r="AB15" s="90"/>
@@ -6788,7 +6788,7 @@
         <v>0.5</v>
       </c>
       <c r="T16" s="99">
-        <f>H16*$L16*$Q16</f>
+        <f t="shared" si="2"/>
         <v>20.941480800000001</v>
       </c>
       <c r="U16" s="28"/>
@@ -6805,11 +6805,11 @@
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
       <c r="Z16" s="94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="AA16" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>GW</v>
       </c>
       <c r="AB16" s="94"/>
@@ -6861,7 +6861,7 @@
         <v>0.3</v>
       </c>
       <c r="T17" s="99">
-        <f>H17*$L17*$Q17</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U17" s="28"/>
@@ -6878,11 +6878,11 @@
         <v>Power Plants Existing00 - Wind energy</v>
       </c>
       <c r="Z17" s="94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="AA17" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>GW</v>
       </c>
       <c r="AB17" s="94"/>
@@ -6929,7 +6929,7 @@
         <v>0.2</v>
       </c>
       <c r="T18" s="99">
-        <f>H18*$L18*$Q18</f>
+        <f t="shared" si="2"/>
         <v>3.42291744</v>
       </c>
       <c r="U18" s="28"/>
@@ -6946,11 +6946,11 @@
         <v>Power Plants Existing00 - Solar energy</v>
       </c>
       <c r="Z18" s="94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>PJ</v>
       </c>
       <c r="AA18" s="94" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>GW</v>
       </c>
       <c r="AB18" s="94"/>
